--- a/XLibur.Tests/Resource/Examples/Styles/StyleIncludeQuotePrefix.xlsx
+++ b/XLibur.Tests/Resource/Examples/Styles/StyleIncludeQuotePrefix.xlsx
@@ -554,9 +554,9 @@
   <x:dimension ref="A1:D20"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="2" width="2.996339" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="9.282054" style="1" customWidth="1"/>
-    <x:col min="4" max="4" width="11.710625" style="1" customWidth="1"/>
+    <x:col min="1" max="2" width="3.139196" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9.853482" style="1" customWidth="1"/>
+    <x:col min="4" max="4" width="12.567768" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4">
